--- a/designer-task-hub/workbook/template.xlsx
+++ b/designer-task-hub/workbook/template.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Dashboard" sheetId="7" r:id="rId21"/>
     <sheet name="Task Details" sheetId="8" r:id="rId22"/>
     <sheet name="Daily Log" sheetId="9" r:id="rId23"/>
+    <sheet name="Task Funnel" sheetId="10" r:id="rId24"/>
   </sheets>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
   <extLst>
@@ -19733,7 +19734,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:P160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -21429,6 +21430,199 @@
       </c>
       <c r="G145" s="60">
         <f>IF($A145="","",SUMIFS(tblTasks[Estimated Effort (Hrs)],tblTasks[Project],$A145))</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Funnel</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awaiting approval</t>
+        </is>
+      </c>
+      <c r="B149" s="12">
+        <f>COUNTIFS('Task Funnel'!$O:$O,$A149)</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changes requested</t>
+        </is>
+      </c>
+      <c r="B150" s="12">
+        <f>COUNTIFS('Task Funnel'!$O:$O,$A150)</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="B151" s="12">
+        <f>COUNTIFS('Task Funnel'!$O:$O,$A151)</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rejected</t>
+        </is>
+      </c>
+      <c r="B152" s="12">
+        <f>COUNTIFS('Task Funnel'!$O:$O,$A152)</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4E Line</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tasks</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Hours</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hours Logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluate</t>
+        </is>
+      </c>
+      <c r="B155" s="12">
+        <f>COUNTIFS('Task Details'!$Q:$Q,$A155)</f>
+      </c>
+      <c r="C155" s="12">
+        <f>B155-COUNTIFS('Task Details'!$Q:$Q,$A155,'Task Details'!$H:$H,"Done*")</f>
+      </c>
+      <c r="D155" s="60">
+        <f>SUMIFS('Task Details'!$I:$I,'Task Details'!$Q:$Q,$A155)</f>
+      </c>
+      <c r="E155" s="60">
+        <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A155)</f>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Educate</t>
+        </is>
+      </c>
+      <c r="B156" s="12">
+        <f>COUNTIFS('Task Details'!$Q:$Q,$A156)</f>
+      </c>
+      <c r="C156" s="12">
+        <f>B156-COUNTIFS('Task Details'!$Q:$Q,$A156,'Task Details'!$H:$H,"Done*")</f>
+      </c>
+      <c r="D156" s="60">
+        <f>SUMIFS('Task Details'!$I:$I,'Task Details'!$Q:$Q,$A156)</f>
+      </c>
+      <c r="E156" s="60">
+        <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A156)</f>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Experience</t>
+        </is>
+      </c>
+      <c r="B157" s="12">
+        <f>COUNTIFS('Task Details'!$Q:$Q,$A157)</f>
+      </c>
+      <c r="C157" s="12">
+        <f>B157-COUNTIFS('Task Details'!$Q:$Q,$A157,'Task Details'!$H:$H,"Done*")</f>
+      </c>
+      <c r="D157" s="60">
+        <f>SUMIFS('Task Details'!$I:$I,'Task Details'!$Q:$Q,$A157)</f>
+      </c>
+      <c r="E157" s="60">
+        <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A157)</f>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enable</t>
+        </is>
+      </c>
+      <c r="B158" s="12">
+        <f>COUNTIFS('Task Details'!$Q:$Q,$A158)</f>
+      </c>
+      <c r="C158" s="12">
+        <f>B158-COUNTIFS('Task Details'!$Q:$Q,$A158,'Task Details'!$H:$H,"Done*")</f>
+      </c>
+      <c r="D158" s="60">
+        <f>SUMIFS('Task Details'!$I:$I,'Task Details'!$Q:$Q,$A158)</f>
+      </c>
+      <c r="E158" s="60">
+        <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A158)</f>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENIE Platform</t>
+        </is>
+      </c>
+      <c r="B159" s="12">
+        <f>COUNTIFS('Task Details'!$Q:$Q,$A159)</f>
+      </c>
+      <c r="C159" s="12">
+        <f>B159-COUNTIFS('Task Details'!$Q:$Q,$A159,'Task Details'!$H:$H,"Done*")</f>
+      </c>
+      <c r="D159" s="60">
+        <f>SUMIFS('Task Details'!$I:$I,'Task Details'!$Q:$Q,$A159)</f>
+      </c>
+      <c r="E159" s="60">
+        <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A159)</f>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
+      <c r="B160" s="12">
+        <f>COUNTIFS('Task Details'!$Q:$Q,$A160)</f>
+      </c>
+      <c r="C160" s="12">
+        <f>B160-COUNTIFS('Task Details'!$Q:$Q,$A160,'Task Details'!$H:$H,"Done*")</f>
+      </c>
+      <c r="D160" s="60">
+        <f>SUMIFS('Task Details'!$I:$I,'Task Details'!$Q:$Q,$A160)</f>
+      </c>
+      <c r="E160" s="60">
+        <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A160)</f>
       </c>
     </row>
   </sheetData>
@@ -21458,7 +21652,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -21477,6 +21671,10 @@
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="36" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21574,9 +21772,29 @@
           <t xml:space="preserve">Brief / Link</t>
         </is>
       </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4E Line</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master Task Title</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request ID</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved On</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P4"/>
+  <autoFilter ref="A4:T4"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21668,4 +21886,141 @@
   <autoFilter ref="A4:J4"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="36" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Funnel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every request PMs submitted, one row per subtask, with your decision. Approved subtasks become Tracker rows (Task ID).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request ID</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submitted</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PM</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4E Line</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master Task</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priority</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtask</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Designer</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Hours</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decided On</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner Note</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:R4"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/designer-task-hub/workbook/template.xlsx
+++ b/designer-task-hub/workbook/template.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Task Details" sheetId="8" r:id="rId22"/>
     <sheet name="Daily Log" sheetId="9" r:id="rId23"/>
     <sheet name="Task Funnel" sheetId="10" r:id="rId24"/>
+    <sheet name="Deliverables" sheetId="11" r:id="rId25"/>
   </sheets>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
   <extLst>
@@ -482,7 +483,7 @@
     <font>
       <b/>
       <sz val="22"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FF111827"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1472,7 +1473,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="0337D8"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1500,7 +1501,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E86A00"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1528,7 +1529,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="7E9CF0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1556,7 +1557,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1F3864"/>
+              <a:srgbClr val="111827"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1708,7 +1709,7 @@
           <c:order val="0"/>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="0337D8"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1855,7 +1856,7 @@
           <c:order val="0"/>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="0337D8"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1868,7 +1869,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="0CA30C"/>
+                <a:srgbClr val="5E8C00"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1881,7 +1882,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="EC835A"/>
+                <a:srgbClr val="E85C24"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1894,7 +1895,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="0337D8"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1920,7 +1921,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="D03B3B"/>
+                <a:srgbClr val="C12400"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1933,7 +1934,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FAB219"/>
+                <a:srgbClr val="FBD300"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -2098,7 +2099,7 @@
           <c:spPr>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="0337D8"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2108,7 +2109,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="0337D8"/>
               </a:solidFill>
               <a:ln w="12700">
                 <a:solidFill>
@@ -2140,7 +2141,7 @@
           <c:spPr>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="E86A00"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2150,7 +2151,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="E86A00"/>
               </a:solidFill>
               <a:ln w="12700">
                 <a:solidFill>
@@ -2182,7 +2183,7 @@
           <c:spPr>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
+                <a:srgbClr val="7E9CF0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2192,7 +2193,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
+                <a:srgbClr val="7E9CF0"/>
               </a:solidFill>
               <a:ln w="12700">
                 <a:solidFill>
@@ -2224,7 +2225,7 @@
           <c:spPr>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="EDA100"/>
+                <a:srgbClr val="C12400"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2234,7 +2235,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="EDA100"/>
+                <a:srgbClr val="C12400"/>
               </a:solidFill>
               <a:ln w="12700">
                 <a:solidFill>
@@ -2266,7 +2267,7 @@
           <c:spPr>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
+                <a:srgbClr val="8A9A1A"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2276,7 +2277,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
+                <a:srgbClr val="8A9A1A"/>
               </a:solidFill>
               <a:ln w="12700">
                 <a:solidFill>
@@ -2434,7 +2435,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="0337D8"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2462,7 +2463,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E86A00"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2618,7 +2619,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="7E9CF0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2646,7 +2647,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="0337D8"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2722,6 +2723,274 @@
         </c:spPr>
         <c:crossAx val="5001"/>
         <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:srgbClr val="E7E6E2"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:solidFill>
+            <a:srgbClr val="52514E"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="262626"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Deliverables completed per week</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$B$163</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0337D8"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$164:$A$171</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$164:$B$171</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$C$163</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E86A00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$164:$A$171</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$C$164:$C$171</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$D$163</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7E9CF0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$164:$A$171</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$D$164:$D$171</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$E$163</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C12400"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$164:$A$171</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$E$164:$E$171</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$F$163</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8A9A1A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$164:$A$171</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$F$164:$F$171</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="70"/>
+        <c:overlap val="-10"/>
+        <c:axId val="5001"/>
+        <c:axId val="5002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="5001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dd-mmm" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="6350">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:crossAx val="5002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="5002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E7E6E2"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:crossAx val="5001"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -2936,6 +3205,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -19734,7 +20033,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P160"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -21623,6 +21922,242 @@
       </c>
       <c r="E160" s="60">
         <f>SUMIFS('Task Details'!$K:$K,'Task Details'!$Q:$Q,$A160)</f>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliverables done, week of</t>
+        </is>
+      </c>
+      <c r="B163" s="5">
+        <f>Scorecard!$A$12</f>
+      </c>
+      <c r="C163" s="5">
+        <f>Scorecard!$A$13</f>
+      </c>
+      <c r="D163" s="5">
+        <f>Scorecard!$A$14</f>
+      </c>
+      <c r="E163" s="5">
+        <f>Scorecard!$A$15</f>
+      </c>
+      <c r="F163" s="5">
+        <f>Scorecard!$A$16</f>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="11">
+        <f>$A$86</f>
+      </c>
+      <c r="B164" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A164,'Deliverables'!$I:$I,"&lt;"&amp;($A164+7)))</f>
+      </c>
+      <c r="C164" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A164,'Deliverables'!$I:$I,"&lt;"&amp;($A164+7)))</f>
+      </c>
+      <c r="D164" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A164,'Deliverables'!$I:$I,"&lt;"&amp;($A164+7)))</f>
+      </c>
+      <c r="E164" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A164,'Deliverables'!$I:$I,"&lt;"&amp;($A164+7)))</f>
+      </c>
+      <c r="F164" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A164,'Deliverables'!$I:$I,"&lt;"&amp;($A164+7)))</f>
+      </c>
+      <c r="G164" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A164,'Deliverables'!$I:$I,"&lt;"&amp;($A164+7))</f>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11">
+        <f>$A$87</f>
+      </c>
+      <c r="B165" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A165,'Deliverables'!$I:$I,"&lt;"&amp;($A165+7)))</f>
+      </c>
+      <c r="C165" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A165,'Deliverables'!$I:$I,"&lt;"&amp;($A165+7)))</f>
+      </c>
+      <c r="D165" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A165,'Deliverables'!$I:$I,"&lt;"&amp;($A165+7)))</f>
+      </c>
+      <c r="E165" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A165,'Deliverables'!$I:$I,"&lt;"&amp;($A165+7)))</f>
+      </c>
+      <c r="F165" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A165,'Deliverables'!$I:$I,"&lt;"&amp;($A165+7)))</f>
+      </c>
+      <c r="G165" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A165,'Deliverables'!$I:$I,"&lt;"&amp;($A165+7))</f>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="11">
+        <f>$A$88</f>
+      </c>
+      <c r="B166" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A166,'Deliverables'!$I:$I,"&lt;"&amp;($A166+7)))</f>
+      </c>
+      <c r="C166" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A166,'Deliverables'!$I:$I,"&lt;"&amp;($A166+7)))</f>
+      </c>
+      <c r="D166" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A166,'Deliverables'!$I:$I,"&lt;"&amp;($A166+7)))</f>
+      </c>
+      <c r="E166" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A166,'Deliverables'!$I:$I,"&lt;"&amp;($A166+7)))</f>
+      </c>
+      <c r="F166" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A166,'Deliverables'!$I:$I,"&lt;"&amp;($A166+7)))</f>
+      </c>
+      <c r="G166" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A166,'Deliverables'!$I:$I,"&lt;"&amp;($A166+7))</f>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11">
+        <f>$A$89</f>
+      </c>
+      <c r="B167" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A167,'Deliverables'!$I:$I,"&lt;"&amp;($A167+7)))</f>
+      </c>
+      <c r="C167" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A167,'Deliverables'!$I:$I,"&lt;"&amp;($A167+7)))</f>
+      </c>
+      <c r="D167" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A167,'Deliverables'!$I:$I,"&lt;"&amp;($A167+7)))</f>
+      </c>
+      <c r="E167" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A167,'Deliverables'!$I:$I,"&lt;"&amp;($A167+7)))</f>
+      </c>
+      <c r="F167" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A167,'Deliverables'!$I:$I,"&lt;"&amp;($A167+7)))</f>
+      </c>
+      <c r="G167" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A167,'Deliverables'!$I:$I,"&lt;"&amp;($A167+7))</f>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="11">
+        <f>$A$90</f>
+      </c>
+      <c r="B168" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A168,'Deliverables'!$I:$I,"&lt;"&amp;($A168+7)))</f>
+      </c>
+      <c r="C168" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A168,'Deliverables'!$I:$I,"&lt;"&amp;($A168+7)))</f>
+      </c>
+      <c r="D168" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A168,'Deliverables'!$I:$I,"&lt;"&amp;($A168+7)))</f>
+      </c>
+      <c r="E168" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A168,'Deliverables'!$I:$I,"&lt;"&amp;($A168+7)))</f>
+      </c>
+      <c r="F168" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A168,'Deliverables'!$I:$I,"&lt;"&amp;($A168+7)))</f>
+      </c>
+      <c r="G168" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A168,'Deliverables'!$I:$I,"&lt;"&amp;($A168+7))</f>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11">
+        <f>$A$91</f>
+      </c>
+      <c r="B169" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A169,'Deliverables'!$I:$I,"&lt;"&amp;($A169+7)))</f>
+      </c>
+      <c r="C169" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A169,'Deliverables'!$I:$I,"&lt;"&amp;($A169+7)))</f>
+      </c>
+      <c r="D169" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A169,'Deliverables'!$I:$I,"&lt;"&amp;($A169+7)))</f>
+      </c>
+      <c r="E169" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A169,'Deliverables'!$I:$I,"&lt;"&amp;($A169+7)))</f>
+      </c>
+      <c r="F169" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A169,'Deliverables'!$I:$I,"&lt;"&amp;($A169+7)))</f>
+      </c>
+      <c r="G169" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A169,'Deliverables'!$I:$I,"&lt;"&amp;($A169+7))</f>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="11">
+        <f>$A$92</f>
+      </c>
+      <c r="B170" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A170,'Deliverables'!$I:$I,"&lt;"&amp;($A170+7)))</f>
+      </c>
+      <c r="C170" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A170,'Deliverables'!$I:$I,"&lt;"&amp;($A170+7)))</f>
+      </c>
+      <c r="D170" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A170,'Deliverables'!$I:$I,"&lt;"&amp;($A170+7)))</f>
+      </c>
+      <c r="E170" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A170,'Deliverables'!$I:$I,"&lt;"&amp;($A170+7)))</f>
+      </c>
+      <c r="F170" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A170,'Deliverables'!$I:$I,"&lt;"&amp;($A170+7)))</f>
+      </c>
+      <c r="G170" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A170,'Deliverables'!$I:$I,"&lt;"&amp;($A170+7))</f>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11">
+        <f>$A$93</f>
+      </c>
+      <c r="B171" s="12">
+        <f>IF(B$163="","",COUNTIFS('Deliverables'!$B:$B,B$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A171,'Deliverables'!$I:$I,"&lt;"&amp;($A171+7)))</f>
+      </c>
+      <c r="C171" s="12">
+        <f>IF(C$163="","",COUNTIFS('Deliverables'!$B:$B,C$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A171,'Deliverables'!$I:$I,"&lt;"&amp;($A171+7)))</f>
+      </c>
+      <c r="D171" s="12">
+        <f>IF(D$163="","",COUNTIFS('Deliverables'!$B:$B,D$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A171,'Deliverables'!$I:$I,"&lt;"&amp;($A171+7)))</f>
+      </c>
+      <c r="E171" s="12">
+        <f>IF(E$163="","",COUNTIFS('Deliverables'!$B:$B,E$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A171,'Deliverables'!$I:$I,"&lt;"&amp;($A171+7)))</f>
+      </c>
+      <c r="F171" s="12">
+        <f>IF(F$163="","",COUNTIFS('Deliverables'!$B:$B,F$163,'Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A171,'Deliverables'!$I:$I,"&lt;"&amp;($A171+7)))</f>
+      </c>
+      <c r="G171" s="12">
+        <f>COUNTIFS('Deliverables'!$H:$H,"Done",'Deliverables'!$I:$I,"&gt;="&amp;$A171,'Deliverables'!$I:$I,"&lt;"&amp;($A171+7))</f>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hours per deliverable</t>
+        </is>
+      </c>
+      <c r="B172" s="60">
+        <f>IF(B$163="","",IFERROR(SUMIFS('Task Details'!$K:$K,'Task Details'!$F:$F,B$163,'Task Details'!$U:$U,"&gt;1")/SUMIFS('Task Details'!$W:$W,'Task Details'!$F:$F,B$163,'Task Details'!$U:$U,"&gt;1"),"-"))</f>
+      </c>
+      <c r="C172" s="60">
+        <f>IF(C$163="","",IFERROR(SUMIFS('Task Details'!$K:$K,'Task Details'!$F:$F,C$163,'Task Details'!$U:$U,"&gt;1")/SUMIFS('Task Details'!$W:$W,'Task Details'!$F:$F,C$163,'Task Details'!$U:$U,"&gt;1"),"-"))</f>
+      </c>
+      <c r="D172" s="60">
+        <f>IF(D$163="","",IFERROR(SUMIFS('Task Details'!$K:$K,'Task Details'!$F:$F,D$163,'Task Details'!$U:$U,"&gt;1")/SUMIFS('Task Details'!$W:$W,'Task Details'!$F:$F,D$163,'Task Details'!$U:$U,"&gt;1"),"-"))</f>
+      </c>
+      <c r="E172" s="60">
+        <f>IF(E$163="","",IFERROR(SUMIFS('Task Details'!$K:$K,'Task Details'!$F:$F,E$163,'Task Details'!$U:$U,"&gt;1")/SUMIFS('Task Details'!$W:$W,'Task Details'!$F:$F,E$163,'Task Details'!$U:$U,"&gt;1"),"-"))</f>
+      </c>
+      <c r="F172" s="60">
+        <f>IF(F$163="","",IFERROR(SUMIFS('Task Details'!$K:$K,'Task Details'!$F:$F,F$163,'Task Details'!$U:$U,"&gt;1")/SUMIFS('Task Details'!$W:$W,'Task Details'!$F:$F,F$163,'Task Details'!$U:$U,"&gt;1"),"-"))</f>
+      </c>
+      <c r="G172" s="60">
+        <f>IFERROR(SUMIFS('Task Details'!$K:$K,'Task Details'!$U:$U,"&gt;1")/SUMIFS('Task Details'!$W:$W,'Task Details'!$U:$U,"&gt;1"),"-")</f>
       </c>
     </row>
   </sheetData>
@@ -21652,7 +22187,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -21675,6 +22210,9 @@
     <col min="18" max="18" width="30" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
     <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21792,9 +22330,24 @@
           <t xml:space="preserve">Approved On</t>
         </is>
       </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qty</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="W4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Items Done</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T4"/>
+  <autoFilter ref="A4:W4"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21890,7 +22443,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -21911,6 +22464,8 @@
     <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="36" customWidth="1"/>
     <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22018,9 +22573,114 @@
           <t xml:space="preserve">Task ID</t>
         </is>
       </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qty</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R4"/>
+  <autoFilter ref="A4:T4"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="5" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliverables</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One row per item inside a batch task (for example each video in a set of 12), written by Design Task Hub on export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task ID</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Designer</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtask</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliverable</t>
+        </is>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done On</t>
+        </is>
+      </c>
+      <c r="J4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revisions</t>
+        </is>
+      </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Link</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K4"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>